--- a/server/master-excel-files/Kailash_PHYSICS_Grade 7.xlsx
+++ b/server/master-excel-files/Kailash_PHYSICS_Grade 7.xlsx
@@ -1,58 +1,132 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\ISAP_PHYSICS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10425"/>
+  </bookViews>
   <sheets>
-    <sheet name="YearPlan" sheetId="1" r:id="rId1"/>
+    <sheet name="Year Plan" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="24">
+  <si>
+    <t>MONTH</t>
+  </si>
+  <si>
+    <t>NCERT SYLLABUS</t>
+  </si>
+  <si>
+    <t>JUNE</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>JULY</t>
+  </si>
+  <si>
+    <t>AUGUST</t>
+  </si>
+  <si>
+    <t>SEPTEMBER</t>
+  </si>
+  <si>
+    <t>OCTOBER</t>
+  </si>
+  <si>
+    <t>SECTION-1</t>
+  </si>
+  <si>
+    <t>SECTION-2</t>
+  </si>
+  <si>
+    <t>SECTION-3</t>
+  </si>
+  <si>
+    <t>SECTION-4</t>
+  </si>
+  <si>
+    <t>SECTION-5</t>
+  </si>
+  <si>
+    <t>SECTION-6</t>
+  </si>
+  <si>
+    <t>IIT SYLLABUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEASUREMENT OF TIME AND MOTION </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EARTH, MOON AND THE SUN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELECTRICITY - CIRCUIT AND ITS COMPONENTS </t>
+  </si>
+  <si>
+    <t>UNITS AND MEASUREMENTS - I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHYSICAL WORLD </t>
+  </si>
+  <si>
+    <t>MOTION IN A STRAIGHT LINE-1</t>
+  </si>
+  <si>
+    <t>UNITS AND MEASUREMENTS - II, MOTION IN A STRAIGHT LINE-1</t>
+  </si>
+  <si>
+    <t>NCERT STATUS</t>
+  </si>
+  <si>
+    <t>IIT STATUS</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -60,18 +134,135 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -150,7 +341,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +375,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +409,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,267 +544,385 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="41.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>MONTH</v>
-      </c>
-      <c r="B1" t="str">
-        <v>NCERT SYLLABUS</v>
-      </c>
-      <c r="C1" t="str">
-        <v>ASSESSMENTS</v>
-      </c>
-      <c r="D1" t="str">
-        <v>IIT SYLLABUS</v>
-      </c>
-      <c r="E1" t="str">
-        <v>SECTION-1</v>
-      </c>
-      <c r="F1" t="str">
-        <v>SECTION-2</v>
-      </c>
-      <c r="G1" t="str">
-        <v>SECTION-3</v>
-      </c>
-      <c r="H1" t="str">
-        <v>SECTION-4</v>
-      </c>
-      <c r="I1" t="str">
-        <v>SECTION-5</v>
-      </c>
-      <c r="J1" t="str">
-        <v>SECTION-6</v>
-      </c>
-      <c r="K1" t="str">
-        <v>STATUS</v>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>JUNE</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v xml:space="preserve">PHYSICAL WORLD </v>
-      </c>
-      <c r="E2" t="str">
-        <v>COMPLETED</v>
-      </c>
-      <c r="F2" t="str">
-        <v>COMPLETED</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="K2" t="str">
-        <v>COMPLETED</v>
-      </c>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>JULY</v>
-      </c>
-      <c r="B3" t="str">
-        <v xml:space="preserve">ELECTRICITY - CIRCUIT AND ITS COMPONENTS </v>
-      </c>
-      <c r="C3" t="str">
-        <v>Periodic Test - 1</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v>IN PROCESS</v>
-      </c>
-      <c r="F3" t="str">
-        <v>IN PROCESS</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="K3" t="str">
-        <v>IN PROCESS</v>
+    <row r="3" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>AUGUST</v>
-      </c>
-      <c r="B4" t="str">
-        <v xml:space="preserve">EARTH, MOON AND THE SUN </v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>UNITS AND MEASUREMENTS - I</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Not Started</v>
+    <row r="4" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>SEPTEMBER</v>
-      </c>
-      <c r="B5" t="str">
-        <v xml:space="preserve">MEASUREMENT OF TIME AND MOTION </v>
-      </c>
-      <c r="C5" t="str">
-        <v>Periodic Test - 2</v>
-      </c>
-      <c r="D5" t="str">
-        <v>UNITS AND MEASUREMENTS - II, MOTION IN A STRAIGHT LINE-1</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Not Started</v>
+    <row r="5" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>OCTOBER</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v>Summative Assessment - 1</v>
-      </c>
-      <c r="D6" t="str">
-        <v>MOTION IN A STRAIGHT LINE-1</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Not Started</v>
-      </c>
-      <c r="K6" t="str">
-        <v>Not Started</v>
+    <row r="6" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
-  </ignoredErrors>
+  <mergeCells count="17">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="F8:G42 C1:I1 C3:I7 K1:Q1 K3:Q7">
+      <formula1>"Not Started,In Progress,Completed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/server/master-excel-files/Kailash_PHYSICS_Grade 7.xlsx
+++ b/server/master-excel-files/Kailash_PHYSICS_Grade 7.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\ISAP_PHYSICS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\Aakash_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="24">
   <si>
     <t>MONTH</t>
   </si>
@@ -45,24 +45,6 @@
     <t>OCTOBER</t>
   </si>
   <si>
-    <t>SECTION-1</t>
-  </si>
-  <si>
-    <t>SECTION-2</t>
-  </si>
-  <si>
-    <t>SECTION-3</t>
-  </si>
-  <si>
-    <t>SECTION-4</t>
-  </si>
-  <si>
-    <t>SECTION-5</t>
-  </si>
-  <si>
-    <t>SECTION-6</t>
-  </si>
-  <si>
     <t>IIT SYLLABUS</t>
   </si>
   <si>
@@ -91,6 +73,24 @@
   </si>
   <si>
     <t>IIT STATUS</t>
+  </si>
+  <si>
+    <t>NCERT_K1</t>
+  </si>
+  <si>
+    <t>NCERT_K2</t>
+  </si>
+  <si>
+    <t>NCERT_K3</t>
+  </si>
+  <si>
+    <t>IIT_K1</t>
+  </si>
+  <si>
+    <t>IIT_K2</t>
+  </si>
+  <si>
+    <t>IIT_K3</t>
   </si>
 </sst>
 </file>
@@ -231,6 +231,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -241,12 +247,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -551,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -559,87 +559,60 @@
     <col min="3" max="3" width="17.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
-    <col min="10" max="10" width="30.7109375" customWidth="1"/>
-    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="30.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="H1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>14</v>
+      <c r="J1" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="4"/>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="6"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="8"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="6"/>
       <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
     </row>
-    <row r="3" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -657,7 +630,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>3</v>
@@ -666,36 +639,18 @@
         <v>3</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="4" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -709,43 +664,25 @@
       <c r="F4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="H4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J4" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="K4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="5" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -760,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>3</v>
@@ -769,52 +706,34 @@
         <v>3</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="6" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="H6" s="1" t="s">
         <v>3</v>
       </c>
@@ -822,31 +741,13 @@
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="7" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,7 +765,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>3</v>
@@ -873,52 +774,28 @@
         <v>3</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="11">
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="F8:G42 C1:I1 C3:I7 K1:Q1 K3:Q7">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="C1:F1 C3:F7 H3:K7 H1:K1">
       <formula1>"Not Started,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/server/master-excel-files/Kailash_PHYSICS_Grade 7.xlsx
+++ b/server/master-excel-files/Kailash_PHYSICS_Grade 7.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="27">
   <si>
     <t>MONTH</t>
   </si>
@@ -69,28 +69,37 @@
     <t>UNITS AND MEASUREMENTS - II, MOTION IN A STRAIGHT LINE-1</t>
   </si>
   <si>
-    <t>NCERT STATUS</t>
-  </si>
-  <si>
     <t>IIT STATUS</t>
   </si>
   <si>
-    <t>NCERT_K1</t>
-  </si>
-  <si>
-    <t>NCERT_K2</t>
-  </si>
-  <si>
-    <t>NCERT_K3</t>
-  </si>
-  <si>
-    <t>IIT_K1</t>
-  </si>
-  <si>
-    <t>IIT_K2</t>
-  </si>
-  <si>
-    <t>IIT_K3</t>
+    <t>NCERT_SEC-1</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-2</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-3</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-4</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-5</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-6</t>
+  </si>
+  <si>
+    <t>IIT_SEC-1</t>
+  </si>
+  <si>
+    <t>IIT_SEC-2</t>
+  </si>
+  <si>
+    <t>IIT_SEC-3</t>
+  </si>
+  <si>
+    <t>NCERT_STATUS</t>
   </si>
 </sst>
 </file>
@@ -551,20 +560,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="41.28515625" customWidth="1"/>
     <col min="3" max="3" width="17.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
-    <col min="7" max="7" width="30.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="5" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -572,47 +581,59 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -630,22 +651,31 @@
         <v>3</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="K3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -664,20 +694,29 @@
       <c r="F4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="H4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="K4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -697,22 +736,31 @@
         <v>3</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="K5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -732,22 +780,31 @@
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="K6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -765,37 +822,49 @@
         <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
+    <mergeCell ref="N1:N2"/>
     <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
     <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="C1:F1 C3:F7 H3:K7 H1:K1">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="K1:N1 K3:N7 C1:I1 C3:I7">
       <formula1>"Not Started,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/server/master-excel-files/Kailash_PHYSICS_Grade 7.xlsx
+++ b/server/master-excel-files/Kailash_PHYSICS_Grade 7.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="28">
   <si>
     <t>MONTH</t>
   </si>
@@ -69,25 +69,28 @@
     <t>UNITS AND MEASUREMENTS - II, MOTION IN A STRAIGHT LINE-1</t>
   </si>
   <si>
+    <t>NCERT STATUS</t>
+  </si>
+  <si>
     <t>IIT STATUS</t>
   </si>
   <si>
-    <t>NCERT_SEC-1</t>
-  </si>
-  <si>
-    <t>NCERT_SEC-2</t>
-  </si>
-  <si>
-    <t>NCERT_SEC-3</t>
-  </si>
-  <si>
-    <t>NCERT_SEC-4</t>
-  </si>
-  <si>
-    <t>NCERT_SEC-5</t>
-  </si>
-  <si>
-    <t>NCERT_SEC-6</t>
+    <t>SEC-1</t>
+  </si>
+  <si>
+    <t>SEC-2</t>
+  </si>
+  <si>
+    <t>SEC-3</t>
+  </si>
+  <si>
+    <t>SEC-4</t>
+  </si>
+  <si>
+    <t>SEC-5</t>
+  </si>
+  <si>
+    <t>SEC-6</t>
   </si>
   <si>
     <t>IIT_SEC-1</t>
@@ -99,7 +102,7 @@
     <t>IIT_SEC-3</t>
   </si>
   <si>
-    <t>NCERT_STATUS</t>
+    <t>IIT_SEC-4</t>
   </si>
 </sst>
 </file>
@@ -560,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -570,10 +573,10 @@
     <col min="5" max="8" width="14.7109375" customWidth="1"/>
     <col min="9" max="9" width="13.140625" customWidth="1"/>
     <col min="10" max="10" width="30.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -581,43 +584,46 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>16</v>
+        <v>26</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="8"/>
@@ -631,9 +637,10 @@
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
-      <c r="N2" s="6"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="6"/>
     </row>
-    <row r="3" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -674,8 +681,11 @@
       <c r="N3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -715,8 +725,11 @@
       <c r="N4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -759,8 +772,11 @@
       <c r="N5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -803,8 +819,11 @@
       <c r="N6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -845,14 +864,18 @@
       <c r="N7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="N1:N2"/>
+  <mergeCells count="15">
+    <mergeCell ref="O1:O2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="M1:M2"/>
-    <mergeCell ref="H1:H2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="I1:I2"/>
@@ -864,7 +887,7 @@
     <mergeCell ref="G1:G2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="K1:N1 K3:N7 C1:I1 C3:I7">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="C3:I7 C1:I1 K3:O7 K1:O1">
       <formula1>"Not Started,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/server/master-excel-files/Kailash_PHYSICS_Grade 7.xlsx
+++ b/server/master-excel-files/Kailash_PHYSICS_Grade 7.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="27">
   <si>
     <t>MONTH</t>
   </si>
@@ -69,28 +69,25 @@
     <t>UNITS AND MEASUREMENTS - II, MOTION IN A STRAIGHT LINE-1</t>
   </si>
   <si>
-    <t>NCERT STATUS</t>
-  </si>
-  <si>
     <t>IIT STATUS</t>
   </si>
   <si>
-    <t>SEC-1</t>
-  </si>
-  <si>
-    <t>SEC-2</t>
-  </si>
-  <si>
-    <t>SEC-3</t>
-  </si>
-  <si>
-    <t>SEC-4</t>
-  </si>
-  <si>
-    <t>SEC-5</t>
-  </si>
-  <si>
-    <t>SEC-6</t>
+    <t>NCERT_SEC-1</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-2</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-3</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-4</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-5</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-6</t>
   </si>
   <si>
     <t>IIT_SEC-1</t>
@@ -102,7 +99,7 @@
     <t>IIT_SEC-3</t>
   </si>
   <si>
-    <t>IIT_SEC-4</t>
+    <t>NCERT_STATUS</t>
   </si>
 </sst>
 </file>
@@ -563,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -573,10 +570,10 @@
     <col min="5" max="8" width="14.7109375" customWidth="1"/>
     <col min="9" max="9" width="13.140625" customWidth="1"/>
     <col min="10" max="10" width="30.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -584,46 +581,43 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="I1" s="5" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>17</v>
+      <c r="N1" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="8"/>
@@ -637,10 +631,9 @@
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="6"/>
+      <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -681,11 +674,8 @@
       <c r="N3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="4" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -725,11 +715,8 @@
       <c r="N4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -772,11 +759,8 @@
       <c r="N5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="6" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -819,11 +803,8 @@
       <c r="N6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="7" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,18 +845,14 @@
       <c r="N7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="O1:O2"/>
+  <mergeCells count="14">
+    <mergeCell ref="N1:N2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
-    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="M1:M2"/>
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="M1:M2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="I1:I2"/>
@@ -887,7 +864,7 @@
     <mergeCell ref="G1:G2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="C3:I7 C1:I1 K3:O7 K1:O1">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="K1:N1 K3:N7 C1:I1 C3:I7">
       <formula1>"Not Started,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/server/master-excel-files/Kailash_PHYSICS_Grade 7.xlsx
+++ b/server/master-excel-files/Kailash_PHYSICS_Grade 7.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\Aakash_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\teacher-year-plan-app\server\master-excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,9 +30,6 @@
     <t>JUNE</t>
   </si>
   <si>
-    <t>Not Started</t>
-  </si>
-  <si>
     <t>JULY</t>
   </si>
   <si>
@@ -100,6 +97,9 @@
   </si>
   <si>
     <t>NCERT_STATUS</t>
+  </si>
+  <si>
+    <t>Not Assigned</t>
   </si>
 </sst>
 </file>
@@ -240,12 +240,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -256,6 +250,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -574,64 +574,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>16</v>
+      <c r="N1" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="6"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="4"/>
     </row>
     <row r="3" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -639,220 +639,215 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="H1:H2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="I1:I2"/>
@@ -862,10 +857,18 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="H1:H2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="K1:N1 K3:N7 C1:I1 C3:I7">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="K1:N1 C1:I1">
       <formula1>"Not Started,In Progress,Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="C3:I7 K3:N7">
+      <formula1>"Not Assigned,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
